--- a/data/trans_dic/P05B_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P05B_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,31</t>
+          <t>1,42; 4,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,39</t>
+          <t>0,42; 2,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,03</t>
+          <t>0,25; 2,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 2,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,72</t>
+          <t>1,76; 4,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,36</t>
+          <t>0,72; 3,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,12</t>
+          <t>1,27; 5,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,74</t>
+          <t>0,35; 3,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,93</t>
+          <t>1,84; 4,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,27</t>
+          <t>0,69; 2,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,97</t>
+          <t>0,88; 2,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,38</t>
+          <t>0,34; 2,03</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,61</t>
+          <t>2,0; 4,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,1</t>
+          <t>0,97; 3,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,76</t>
+          <t>0,7; 2,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,62</t>
+          <t>0,79; 4,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,63</t>
+          <t>3,15; 6,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,04</t>
+          <t>0,98; 3,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,52</t>
+          <t>1,05; 3,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,88</t>
+          <t>0,51; 2,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,97</t>
+          <t>2,73; 4,96</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,76</t>
+          <t>1,2; 2,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,64</t>
+          <t>1,12; 2,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,02</t>
+          <t>0,89; 2,94</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,59</t>
+          <t>2,3; 5,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,51</t>
+          <t>1,08; 3,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,31</t>
+          <t>0,45; 2,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,51</t>
+          <t>0,34; 2,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 7,79</t>
+          <t>4,22; 7,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,42</t>
+          <t>1,13; 3,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,37</t>
+          <t>1,06; 3,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,7</t>
+          <t>0,27; 1,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,09</t>
+          <t>3,7; 5,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,04</t>
+          <t>1,28; 2,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,34</t>
+          <t>0,94; 2,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,69</t>
+          <t>0,45; 1,64</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,58</t>
+          <t>0,96; 3,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,98</t>
+          <t>1,24; 4,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,36</t>
+          <t>0,77; 3,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,29</t>
+          <t>0,16; 1,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,09</t>
+          <t>2,68; 6,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,71</t>
+          <t>0,52; 2,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,21</t>
+          <t>0,89; 3,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,84</t>
+          <t>0,57; 1,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,24</t>
+          <t>2,05; 4,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,93</t>
+          <t>1,16; 2,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,76</t>
+          <t>1,08; 2,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,19</t>
+          <t>0,49; 1,36</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,33</t>
+          <t>2,21; 6,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1287,52 +1287,52 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,7</t>
+          <t>0,44; 2,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,75</t>
+          <t>0,63; 2,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,59</t>
+          <t>3,01; 7,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,86</t>
+          <t>0,48; 2,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,99</t>
+          <t>0,48; 2,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,52</t>
+          <t>0,92; 2,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,95</t>
+          <t>2,87; 5,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,3</t>
+          <t>0,69; 2,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,29</t>
+          <t>0,7; 2,42</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,26</t>
+          <t>0,95; 2,17</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,63</t>
+          <t>0,29; 2,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>0,0; 2,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,33</t>
+          <t>0,32; 3,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,66</t>
+          <t>0,74; 2,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,97; 8,49</t>
+          <t>3,76; 8,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 2,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,17</t>
+          <t>1,05; 4,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,02</t>
+          <t>0,96; 2,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,38</t>
+          <t>2,46; 5,1</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,57</t>
+          <t>0,15; 1,91</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,05</t>
+          <t>0,93; 3,21</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,89</t>
+          <t>0,98; 2,3</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,4; 7,85</t>
+          <t>2,45; 8,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,92</t>
+          <t>0,43; 3,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,28</t>
+          <t>0,95; 4,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,2</t>
+          <t>0,19; 1,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 6,98</t>
+          <t>2,07; 6,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,3</t>
+          <t>1,13; 4,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,95</t>
+          <t>1,51; 5,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,2</t>
+          <t>0,61; 2,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,65; 6,31</t>
+          <t>2,9; 6,39</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,43</t>
+          <t>1,05; 3,49</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,61</t>
+          <t>1,6; 4,47</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,7</t>
+          <t>0,61; 1,72</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,38; 3,61</t>
+          <t>2,42; 3,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,17</t>
+          <t>1,23; 2,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,86</t>
+          <t>0,98; 1,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,61</t>
+          <t>0,8; 1,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,02; 5,43</t>
+          <t>4,0; 5,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,09</t>
+          <t>1,22; 2,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,75</t>
+          <t>1,67; 2,68</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,59</t>
+          <t>0,99; 1,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,37; 4,35</t>
+          <t>3,38; 4,35</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,35; 1,97</t>
+          <t>1,35; 2,03</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,1</t>
+          <t>1,45; 2,13</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,42</t>
+          <t>0,95; 1,43</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t>7302</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6495; 21306</t>
+          <t>7012; 22043</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1900; 10829</t>
+          <t>1889; 10662</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1049; 8519</t>
+          <t>1042; 9008</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 12277</t>
+          <t>0; 8826</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8404; 22058</t>
+          <t>8208; 22186</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3109; 14470</t>
+          <t>3082; 14663</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5845; 20118</t>
+          <t>4994; 20352</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1609; 14839</t>
+          <t>1256; 13612</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17853; 37762</t>
+          <t>17704; 38931</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6765; 20052</t>
+          <t>6083; 20393</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8283; 24145</t>
+          <t>7119; 23218</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2548; 17000</t>
+          <t>2614; 15641</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9464</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6630</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16321</t>
+          <t>15999</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13425; 33877</t>
+          <t>14680; 35503</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6613; 21206</t>
+          <t>6645; 22577</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4124; 16227</t>
+          <t>4127; 16033</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3110; 19553</t>
+          <t>3761; 21164</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19499; 41392</t>
+          <t>19677; 41749</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5898; 18535</t>
+          <t>5954; 19485</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6212; 19782</t>
+          <t>5881; 19899</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2336; 14741</t>
+          <t>2544; 13688</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38597; 67582</t>
+          <t>37150; 67478</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15512; 35666</t>
+          <t>15568; 34221</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12342; 30353</t>
+          <t>12862; 30085</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8849; 28236</t>
+          <t>8670; 28740</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10503</t>
+          <t>10758</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14267; 35711</t>
+          <t>14679; 36090</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7305; 23914</t>
+          <t>7376; 23695</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3038; 15459</t>
+          <t>3019; 13670</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2241; 13422</t>
+          <t>2108; 14547</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>28835; 53745</t>
+          <t>29137; 54529</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7332; 24268</t>
+          <t>8000; 23491</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7351; 22231</t>
+          <t>6980; 21104</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1808; 10071</t>
+          <t>1686; 10840</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>47899; 80964</t>
+          <t>49211; 79568</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18422; 42271</t>
+          <t>17840; 40858</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13069; 31083</t>
+          <t>12478; 31258</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5579; 19070</t>
+          <t>5555; 20306</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>8384</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11703</t>
+          <t>12504</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5029; 18574</t>
+          <t>5000; 18699</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7724; 24428</t>
+          <t>7607; 25536</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4959; 21648</t>
+          <t>4972; 21175</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>957; 11420</t>
+          <t>1118; 10111</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14013; 31413</t>
+          <t>13821; 31492</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3149; 16698</t>
+          <t>3215; 17114</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6526; 20863</t>
+          <t>5804; 20742</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4074; 13084</t>
+          <t>4219; 13902</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20720; 43824</t>
+          <t>21181; 44870</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14643; 35948</t>
+          <t>14270; 35301</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13392; 35618</t>
+          <t>13935; 37356</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5631; 18970</t>
+          <t>7100; 19445</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>8274</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8588</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16921</t>
+          <t>17959</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8420; 24439</t>
+          <t>8517; 23723</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2015; 11603</t>
+          <t>2032; 11591</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2107; 12798</t>
+          <t>2097; 13048</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4040; 15383</t>
+          <t>3826; 15045</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12184; 30676</t>
+          <t>12160; 30016</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2941; 12673</t>
+          <t>2136; 12749</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2389; 14744</t>
+          <t>2367; 14120</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4730; 13765</t>
+          <t>5560; 15442</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23782; 46980</t>
+          <t>22689; 46948</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6188; 20015</t>
+          <t>5973; 20436</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6715; 22141</t>
+          <t>6781; 23405</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11086; 25036</t>
+          <t>11601; 26343</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>6037</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>6732</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11889</t>
+          <t>12947</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>813; 7698</t>
+          <t>837; 8522</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6939</t>
+          <t>0; 6974</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1050; 11141</t>
+          <t>1055; 12219</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2433; 9780</t>
+          <t>2992; 11352</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13621; 29121</t>
+          <t>12899; 30316</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 9704</t>
+          <t>0; 9647</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4034; 15702</t>
+          <t>3972; 15435</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2006; 12258</t>
+          <t>4175; 11616</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16338; 34172</t>
+          <t>15660; 32402</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>984; 10355</t>
+          <t>991; 12567</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6929; 21682</t>
+          <t>6603; 22857</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5259; 18367</t>
+          <t>8266; 19368</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>5578</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>7591</t>
+          <t>8004</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4970; 16218</t>
+          <t>5058; 16533</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1045; 9720</t>
+          <t>1059; 9364</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2419; 11003</t>
+          <t>2446; 11449</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>582; 6195</t>
+          <t>592; 5828</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7054; 23304</t>
+          <t>6908; 22321</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4253; 16450</t>
+          <t>4311; 16733</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6169; 23561</t>
+          <t>5987; 23649</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2677; 9293</t>
+          <t>2834; 10081</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14300; 34103</t>
+          <t>15656; 34537</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6494; 21625</t>
+          <t>6623; 21983</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10455; 30144</t>
+          <t>10451; 29178</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4233; 12012</t>
+          <t>4730; 13287</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>37165</t>
+          <t>37868</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>45413</t>
+          <t>47605</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>82578</t>
+          <t>85473</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>77821; 118038</t>
+          <t>79226; 119159</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>42992; 73995</t>
+          <t>42094; 72273</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>33487; 62825</t>
+          <t>33076; 61293</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>25729; 55549</t>
+          <t>28070; 53861</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>135783; 183332</t>
+          <t>135032; 183299</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>42825; 73961</t>
+          <t>43147; 74619</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>59492; 97187</t>
+          <t>58836; 94563</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>33726; 59068</t>
+          <t>36797; 60395</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>224001; 289091</t>
+          <t>225037; 289010</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>93701; 137168</t>
+          <t>94193; 141390</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>100222; 145077</t>
+          <t>100422; 147346</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>65425; 101869</t>
+          <t>68745; 103457</t>
         </is>
       </c>
     </row>
